--- a/protocol/PowerHub.xlsx
+++ b/protocol/PowerHub.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28860" windowHeight="16460"/>
+    <workbookView windowWidth="20460"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -697,8 +697,8 @@
 Day: 1-31
 Month: 1-12
 Year: 0-99
-Week Day:0x01, Sunday; 0x02, Monday; 0x04, Tuesday; 0x08, Wednesday;
-0x10: Thursday; 0x20: Friday; 0x40: Saturday; 0x80: Sunday</t>
+Week Day:0x01, Sunday; 02, Monday; 04, Tuesday; 08, Wednesday;
+10: Thursday; 20: Friday; 40: Saturday; 80: Sunday</t>
   </si>
   <si>
     <t>RTC Alarm</t>
@@ -2243,7 +2243,7 @@
       <c r="S2" s="5"/>
       <c r="T2" s="42"/>
       <c r="U2" s="45">
-        <v>45946</v>
+        <v>45972</v>
       </c>
     </row>
     <row r="3" ht="33" customHeight="1" spans="1:21">
